--- a/artfynd/A 10236-2026 artfynd.xlsx
+++ b/artfynd/A 10236-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82984646</v>
+        <v>6899003</v>
       </c>
       <c r="B3" t="n">
-        <v>90005</v>
+        <v>95511</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,37 +808,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>221944</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Baståsen S, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564046.7840100565</v>
+        <v>563901.1745636133</v>
       </c>
       <c r="R3" t="n">
-        <v>6618844.652405529</v>
+        <v>6618902.731078749</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +873,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-03-21</t>
+          <t>2013-08-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -875,7 +883,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-03-21</t>
+          <t>2013-08-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -889,18 +897,17 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Grandominerad skog</t>
+          <t>Blandsumpskog.</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>På mossig sten, invid skogsbäck.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -918,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82984714</v>
+        <v>82984646</v>
       </c>
       <c r="B4" t="n">
-        <v>89588</v>
+        <v>90005</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1106</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1015,11 +1022,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1030,7 +1033,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1045,6 +1048,136 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>82984714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>89588</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Baståsen S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>564046.7840100565</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6618844.652405529</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-03-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-03-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Grandominerad skog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10236-2026 artfynd.xlsx
+++ b/artfynd/A 10236-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4225751</v>
+        <v>82984714</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>1106</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Baståsen S, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564051.3196214428</v>
+        <v>564047</v>
       </c>
       <c r="R2" t="n">
-        <v>6618875.017071676</v>
+        <v>6618845</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-05-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-03-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-05-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-03-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,12 +757,22 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Blandskogskärr, gran, klibbal, björk</t>
+          <t>Grandominerad skog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6899003</v>
+        <v>82984646</v>
       </c>
       <c r="B3" t="n">
-        <v>95511</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,45 +801,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Baståsen S, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563901.1745636133</v>
+        <v>564047</v>
       </c>
       <c r="R3" t="n">
-        <v>6618902.731078749</v>
+        <v>6618845</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,22 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-08-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-03-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-08-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-03-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,17 +872,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Blandsumpskog.</t>
+          <t>Grandominerad skog</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>På mossig sten, invid skogsbäck.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -925,15 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82984646</v>
+        <v>116237373</v>
       </c>
       <c r="B4" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -968,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564046.7840100565</v>
+        <v>563890</v>
       </c>
       <c r="R4" t="n">
-        <v>6618844.652405529</v>
+        <v>6619016</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,22 +969,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-03-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-03-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,12 +989,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Grandominerad skog</t>
+          <t>Sumpskog, klibbal, gran, björk, skogsbäck</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Grov granlåga, med klibbticka</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1051,56 +1012,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>82984714</v>
+        <v>2436957</v>
       </c>
       <c r="B5" t="n">
-        <v>89588</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1106</v>
+        <v>220075</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Baståsen S, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564046.7840100565</v>
+        <v>563915</v>
       </c>
       <c r="R5" t="n">
-        <v>6618844.652405529</v>
+        <v>6618993</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,22 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-03-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-05-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-03-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-05-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,22 +1096,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Grandominerad skog</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>Blandskogskärr gran, klibbal, björk</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1178,6 +1116,981 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2436958</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Baståsen S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>563920</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6618958</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2013-05-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2013-05-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Blandskogskärr gran, klibbal, björk</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2436959</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Baståsen S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>563941</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6618929</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2013-05-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2013-05-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Blandskogskärr gran, klibbal, björk</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2436960</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Baståsen S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>564051</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6618875</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2013-05-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2013-05-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Blandskogskärr, gran, klibbal, björk</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2436961</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Baståsen S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>563970</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6618964</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2013-05-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2013-05-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Blandskogskärr, gran, klibbal, björk</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2436962</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Baståsen S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>563960</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6618983</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2013-05-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2013-05-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Blandskogskärr, gran, klibbal, björk</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>116237175</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Baståsen S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>564007</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6618908</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-04-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Sumpskog, klibbal, gran, björk</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6894035</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Baståsen S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>563983</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6618960</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2013-08-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2013-08-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Blandsumpskog, källdragspåverkad.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tom Sävström, Einar Marklund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6899003</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Baståsen S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>563901</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6618903</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2013-08-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2013-08-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Blandsumpskog.</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>På mossig sten, invid skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4225751</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Baståsen S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>564051</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6618875</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2013-05-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2013-05-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Blandskogskärr, gran, klibbal, björk</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10236-2026 artfynd.xlsx
+++ b/artfynd/A 10236-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82984714</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82984646</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116237373</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2436957</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2436958</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,6 +1360,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2436959</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1437,6 +1472,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2436960</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1544,6 +1584,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2436961</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1651,6 +1696,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2436962</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116237175</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1875,6 +1930,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6894035</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1989,6 +2049,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6899003</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2091,8 +2156,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4225751</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>